--- a/fix-errors/ig/FRInformantLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRInformantLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-informant|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-informant</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-informant|0.1.0</t>
   </si>
   <si>
     <t>FRLMInformant</t>
